--- a/data/trans_orig/P6903-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6903-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23879</t>
+          <t>24857</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16996</t>
+          <t>17118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20139</t>
+          <t>19995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37650</t>
+          <t>37130</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>51,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18965</t>
+          <t>17987</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32215</t>
+          <t>31845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22221</t>
+          <t>22574</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33813</t>
+          <t>34333</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51324</t>
+          <t>51468</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>72,02%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14261</t>
+          <t>13577</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31884</t>
+          <t>30859</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14740</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22594</t>
+          <t>23270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42475</t>
+          <t>43543</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40513</t>
+          <t>41538</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58136</t>
+          <t>58820</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17948</t>
+          <t>17064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27849</t>
+          <t>27670</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62609</t>
+          <t>61541</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>82490</t>
+          <t>81814</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>77,86%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19110</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7889</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22912</t>
+          <t>22879</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,22%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17505</t>
+          <t>17571</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29744</t>
+          <t>29452</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>14758</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20749</t>
+          <t>20751</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35427</t>
+          <t>35460</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49165</t>
+          <t>49118</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,19%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18920</t>
+          <t>19128</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>946</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>7680</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>8474</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22789</t>
+          <t>23709</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>39195</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52636</t>
+          <t>52511</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15054</t>
+          <t>15026</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21773</t>
+          <t>21760</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58240</t>
+          <t>57320</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72683</t>
+          <t>72555</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,54%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>11412</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15023</t>
+          <t>14816</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,51%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11021</t>
+          <t>11542</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19540</t>
+          <t>19638</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14902</t>
+          <t>15109</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25237</t>
+          <t>25191</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,18%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>11390</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24786</t>
+          <t>24941</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12162</t>
+          <t>12207</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26293</t>
+          <t>26991</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>48,28%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17024</t>
+          <t>16869</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30356</t>
+          <t>30420</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9826</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29610</t>
+          <t>28912</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43741</t>
+          <t>43696</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,16%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16928</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33852</t>
+          <t>33751</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19487</t>
+          <t>19824</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28607</t>
+          <t>28623</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49213</t>
+          <t>50227</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>38,06%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54596</t>
+          <t>54697</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>71520</t>
+          <t>71449</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24048</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>35627</t>
+          <t>35929</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>82770</t>
+          <t>81756</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>103376</t>
+          <t>103360</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,31%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26420</t>
+          <t>26397</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46319</t>
+          <t>45841</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>17680</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31616</t>
+          <t>31380</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>48311</t>
+          <t>48815</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>73730</t>
+          <t>73211</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,13%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>62596</t>
+          <t>63074</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>82495</t>
+          <t>82518</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18170</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32498</t>
+          <t>32106</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>84971</t>
+          <t>85490</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>110390</t>
+          <t>109886</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,24%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>128890</t>
+          <t>129613</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>170546</t>
+          <t>170683</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>55237</t>
+          <t>54919</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>83314</t>
+          <t>81376</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>192224</t>
+          <t>192104</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>242444</t>
+          <t>242897</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>301759</t>
+          <t>301622</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>343415</t>
+          <t>342692</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>136807</t>
+          <t>138745</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>164884</t>
+          <t>165202</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>449983</t>
+          <t>449530</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>500203</t>
+          <t>500323</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,26%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2012 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>18416</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11820</t>
+          <t>11739</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22960</t>
+          <t>23084</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21399</t>
+          <t>21543</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38277</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,96%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20015</t>
+          <t>21078</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32784</t>
+          <t>33187</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18325</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31183</t>
+          <t>31362</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48240</t>
+          <t>48096</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>11744</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26088</t>
+          <t>25884</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>3784</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14508</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18210</t>
+          <t>17814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36918</t>
+          <t>37168</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30502</t>
+          <t>30706</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45357</t>
+          <t>44846</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19807</t>
+          <t>19969</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30993</t>
+          <t>30531</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53987</t>
+          <t>53737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72695</t>
+          <t>73091</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,4%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>924</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>9457</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14700</t>
+          <t>14500</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17805</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24387</t>
+          <t>24381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8987</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>15994</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28540</t>
+          <t>28740</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38542</t>
+          <t>39251</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19383</t>
+          <t>19703</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19101</t>
+          <t>18473</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>17227</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34167</t>
+          <t>33803</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25477</t>
+          <t>25157</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>37918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21598</t>
+          <t>21782</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40228</t>
+          <t>40592</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57333</t>
+          <t>57168</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,84%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>935</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>10528</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10420</t>
+          <t>10263</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10702</t>
+          <t>10726</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16993</t>
+          <t>16260</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24926</t>
+          <t>24837</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14035</t>
+          <t>14086</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19845</t>
+          <t>19579</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29345</t>
+          <t>29294</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40375</t>
+          <t>39666</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14024</t>
+          <t>14182</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38985</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51779</t>
+          <t>51708</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>14728</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>18448</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>13054</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29417</t>
+          <t>28356</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39564</t>
+          <t>39702</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50419</t>
+          <t>50372</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28195</t>
+          <t>27932</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39619</t>
+          <t>39537</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>71393</t>
+          <t>72454</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>87726</t>
+          <t>87756</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,05%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21638</t>
+          <t>21190</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>17017</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17305</t>
+          <t>17411</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34340</t>
+          <t>34281</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,93%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23481</t>
+          <t>23929</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36438</t>
+          <t>36795</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>12505</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24488</t>
+          <t>24145</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>40301</t>
+          <t>40360</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>57336</t>
+          <t>57230</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,67%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>62308</t>
+          <t>63279</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>92651</t>
+          <t>93865</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>61107</t>
+          <t>61476</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>89027</t>
+          <t>88549</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>132031</t>
+          <t>129351</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>174382</t>
+          <t>175264</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>231652</t>
+          <t>230438</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>261995</t>
+          <t>261024</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>125651</t>
+          <t>126129</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>153571</t>
+          <t>153202</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>364599</t>
+          <t>363717</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>406950</t>
+          <t>409630</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>76,0%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16488</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33094</t>
+          <t>33085</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13878</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26038</t>
+          <t>26347</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35408</t>
+          <t>33785</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55023</t>
+          <t>55789</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>56,09%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25483</t>
+          <t>25492</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42089</t>
+          <t>41550</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14846</t>
+          <t>14537</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>27350</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44438</t>
+          <t>43672</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64053</t>
+          <t>65676</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>66,03%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24862</t>
+          <t>25787</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42994</t>
+          <t>44072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18876</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31833</t>
+          <t>31982</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49545</t>
+          <t>49039</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71857</t>
+          <t>71290</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>56,81%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39792</t>
+          <t>38714</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57924</t>
+          <t>56999</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>10715</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23821</t>
+          <t>23830</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53626</t>
+          <t>54193</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75938</t>
+          <t>76444</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,92%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>12129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11906</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19547</t>
+          <t>19528</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22563</t>
+          <t>21626</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31033</t>
+          <t>31053</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9968</t>
+          <t>10276</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>21820</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20069</t>
+          <t>19360</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23188</t>
+          <t>22786</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39226</t>
+          <t>38778</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,14%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10722</t>
+          <t>10645</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22497</t>
+          <t>22189</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21141</t>
+          <t>21480</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23174</t>
+          <t>23622</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39212</t>
+          <t>39614</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>63,48%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>11424</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>916</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15493</t>
+          <t>15767</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>76,39%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11789</t>
+          <t>11561</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>785</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>70,34%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14375</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>18940</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>63,43%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>7848</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17448</t>
+          <t>17499</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>931</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>10920</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>22238</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>74,47%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33974</t>
+          <t>34897</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>11382</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25038</t>
+          <t>25481</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31829</t>
+          <t>31153</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53406</t>
+          <t>53763</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>40,11%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44368</t>
+          <t>43445</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>61669</t>
+          <t>61767</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30644</t>
+          <t>30201</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44379</t>
+          <t>44300</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>80618</t>
+          <t>80261</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>102195</t>
+          <t>102871</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20425</t>
+          <t>20564</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10873</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>25073</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,32%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18849</t>
+          <t>18710</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30689</t>
+          <t>30711</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12817</t>
+          <t>13001</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20476</t>
+          <t>20444</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35833</t>
+          <t>35601</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>49801</t>
+          <t>49953</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>117870</t>
+          <t>117715</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>154859</t>
+          <t>156230</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>76669</t>
+          <t>74264</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>105873</t>
+          <t>103788</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>202214</t>
+          <t>202638</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>250839</t>
+          <t>251475</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,41%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>195142</t>
+          <t>193771</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>232131</t>
+          <t>232286</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>110425</t>
+          <t>112510</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>139629</t>
+          <t>142034</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>315460</t>
+          <t>314824</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>364085</t>
+          <t>363661</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,22%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2023 (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9604</t>
+          <t>10411</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>8194</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>15639</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14465</t>
+          <t>13658</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22923</t>
+          <t>22599</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25217</t>
+          <t>24185</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35382</t>
+          <t>35146</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,25%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11120</t>
+          <t>10898</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28194</t>
+          <t>28898</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14823</t>
+          <t>14458</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26200</t>
+          <t>26127</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29905</t>
+          <t>29140</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50566</t>
+          <t>50097</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,62%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18086</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35160</t>
+          <t>35382</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19243</t>
+          <t>19316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30620</t>
+          <t>30985</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41157</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61818</t>
+          <t>62583</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>68,23%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>10539</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18155</t>
+          <t>17979</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11684</t>
+          <t>11330</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25116</t>
+          <t>24267</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38872</t>
+          <t>38956</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47649</t>
+          <t>47721</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27771</t>
+          <t>27947</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37445</t>
+          <t>37726</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>70306</t>
+          <t>71155</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>83738</t>
+          <t>84092</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>88,13%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>12296</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27989</t>
+          <t>29175</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>9768</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54403</t>
+          <t>54994</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23116</t>
+          <t>24516</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74078</t>
+          <t>73981</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,14%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12364</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27969</t>
+          <t>28057</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26249</t>
+          <t>25658</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70376</t>
+          <t>70884</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46927</t>
+          <t>47024</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>97889</t>
+          <t>96489</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>79,74%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5510</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>11437</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16408</t>
+          <t>16440</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18568</t>
+          <t>18560</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25046</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>90,23%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13060</t>
+          <t>12904</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10925</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22816</t>
+          <t>23006</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18556</t>
+          <t>18712</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27322</t>
+          <t>27311</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17946</t>
+          <t>17350</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25514</t>
+          <t>24886</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>39015</t>
+          <t>38825</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50906</t>
+          <t>50737</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,06%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23413</t>
+          <t>23014</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20785</t>
+          <t>20645</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34936</t>
+          <t>35093</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33797</t>
+          <t>33832</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53540</t>
+          <t>53666</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47793</t>
+          <t>48192</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>62359</t>
+          <t>62091</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34910</t>
+          <t>34753</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49061</t>
+          <t>49201</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>87512</t>
+          <t>87386</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>107255</t>
+          <t>107220</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,01%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32505</t>
+          <t>32241</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46735</t>
+          <t>45974</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25416</t>
+          <t>25531</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40361</t>
+          <t>40757</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61674</t>
+          <t>62149</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>81967</t>
+          <t>82581</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>74,09%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10022</t>
+          <t>10783</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24252</t>
+          <t>24516</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14349</t>
+          <t>13953</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29294</t>
+          <t>29179</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29500</t>
+          <t>28886</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>49793</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,24%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>96638</t>
+          <t>96204</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>137275</t>
+          <t>133498</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>99999</t>
+          <t>101182</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>160985</t>
+          <t>160700</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>214441</t>
+          <t>209245</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>282906</t>
+          <t>282302</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>199580</t>
+          <t>203357</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>240217</t>
+          <t>240651</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>192549</t>
+          <t>192834</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>253535</t>
+          <t>252352</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>407483</t>
+          <t>408087</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>475948</t>
+          <t>481144</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,69%</t>
         </is>
       </c>
     </row>
